--- a/data/trans_dic/P37A$medicoenfermedad-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P37A$medicoenfermedad-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,19; 8,43</t>
+          <t>2,99; 8,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,09</t>
+          <t>1,18; 4,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,03; 9,19</t>
+          <t>3,07; 9,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 6,04</t>
+          <t>2,26; 6,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,99</t>
+          <t>0,61; 4,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,96</t>
+          <t>1,07; 5,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 6,76</t>
+          <t>1,8; 6,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,85</t>
+          <t>1,77; 4,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,36</t>
+          <t>2,15; 5,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,12</t>
+          <t>1,46; 4,13</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,08; 6,66</t>
+          <t>2,99; 6,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 4,91</t>
+          <t>2,44; 4,7</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,83</t>
+          <t>2,29; 5,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,93; 7,31</t>
+          <t>3,0; 7,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,48; 8,01</t>
+          <t>3,34; 7,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,49</t>
+          <t>2,04; 5,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,45</t>
+          <t>1,73; 4,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,61; 7,41</t>
+          <t>3,78; 7,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 5,06</t>
+          <t>1,9; 5,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,6</t>
+          <t>1,86; 4,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 4,73</t>
+          <t>2,42; 4,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,77; 6,71</t>
+          <t>3,65; 6,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,03; 5,54</t>
+          <t>2,99; 5,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,44</t>
+          <t>2,28; 4,36</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 7,4</t>
+          <t>2,5; 7,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 6,16</t>
+          <t>1,52; 5,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,57</t>
+          <t>1,64; 5,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,26</t>
+          <t>2,49; 6,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,06</t>
+          <t>0,3; 3,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,54</t>
+          <t>1,49; 5,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,4</t>
+          <t>1,48; 5,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,39</t>
+          <t>2,14; 5,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,34</t>
+          <t>1,75; 4,43</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,92</t>
+          <t>1,88; 4,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,77</t>
+          <t>1,81; 4,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,3</t>
+          <t>2,67; 5,15</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,67</t>
+          <t>0,78; 3,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 6,87</t>
+          <t>2,19; 6,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,28; 9,37</t>
+          <t>4,34; 9,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,18; 11,23</t>
+          <t>3,65; 9,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,75; 6,93</t>
+          <t>2,81; 6,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 6,82</t>
+          <t>2,83; 7,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 10,14</t>
+          <t>4,84; 10,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,73; 8,84</t>
+          <t>5,68; 10,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,8</t>
+          <t>2,09; 4,73</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,89</t>
+          <t>2,84; 5,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,9; 8,81</t>
+          <t>5,07; 9,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 8,83</t>
+          <t>5,41; 8,91</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,22; 8,57</t>
+          <t>2,44; 8,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 7,18</t>
+          <t>1,51; 6,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 6,51</t>
+          <t>1,21; 6,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,52; 11,93</t>
+          <t>5,05; 10,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,4; 10,18</t>
+          <t>3,09; 9,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,73; 10,5</t>
+          <t>3,69; 10,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,14</t>
+          <t>0,51; 4,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,82; 12,52</t>
+          <t>8,45; 13,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 8,23</t>
+          <t>3,46; 8,27</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 7,67</t>
+          <t>3,43; 7,58</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,7</t>
+          <t>1,27; 4,51</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,03; 10,99</t>
+          <t>7,5; 11,47</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,21</t>
+          <t>1,08; 5,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,28; 7,24</t>
+          <t>2,28; 7,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,24</t>
+          <t>0,98; 4,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,1</t>
+          <t>2,35; 6,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,09</t>
+          <t>0,7; 3,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,88; 8,42</t>
+          <t>2,94; 8,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,81</t>
+          <t>0,37; 3,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,29</t>
+          <t>1,43; 4,51</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,8</t>
+          <t>1,26; 3,69</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,05; 6,69</t>
+          <t>3,04; 6,61</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,31</t>
+          <t>0,92; 3,43</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,68</t>
+          <t>2,23; 4,57</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,74</t>
+          <t>1,84; 4,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,37; 5,36</t>
+          <t>2,37; 5,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,66</t>
+          <t>1,31; 3,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,67; 9,72</t>
+          <t>5,72; 9,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,3</t>
+          <t>1,02; 3,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,97; 6,14</t>
+          <t>2,91; 6,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,95</t>
+          <t>1,53; 4,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,88; 8,46</t>
+          <t>6,64; 9,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,46</t>
+          <t>1,79; 3,61</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,96; 5,27</t>
+          <t>2,98; 5,13</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,44</t>
+          <t>1,79; 3,41</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,16; 8,27</t>
+          <t>6,72; 9,22</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,57</t>
+          <t>2,02; 4,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,9</t>
+          <t>2,05; 4,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,82</t>
+          <t>0,92; 2,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,06; 7,14</t>
+          <t>4,88; 8,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,56</t>
+          <t>1,94; 4,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,77</t>
+          <t>1,4; 3,59</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,28</t>
+          <t>1,04; 3,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,3; 10,62</t>
+          <t>7,39; 10,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,06</t>
+          <t>2,32; 4,07</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,84</t>
+          <t>1,93; 3,78</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,61</t>
+          <t>1,23; 2,65</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,24</t>
+          <t>6,56; 8,91</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,1</t>
+          <t>2,86; 4,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,04; 4,37</t>
+          <t>3,04; 4,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,88; 4,15</t>
+          <t>2,86; 4,13</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,18; 6,16</t>
+          <t>4,93; 6,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,4</t>
+          <t>2,24; 3,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,37; 4,68</t>
+          <t>3,27; 4,64</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,64</t>
+          <t>2,45; 3,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,63; 6,43</t>
+          <t>5,72; 6,97</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,71; 3,55</t>
+          <t>2,7; 3,5</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3,38; 4,36</t>
+          <t>3,36; 4,37</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,84; 3,67</t>
+          <t>2,87; 3,7</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,75; 6,09</t>
+          <t>5,54; 6,49</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11614</t>
+          <t>12605</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8895</t>
+          <t>9221</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20510</t>
+          <t>21826</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8715; 23027</t>
+          <t>8164; 22627</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3475; 14998</t>
+          <t>3473; 14372</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8886; 26995</t>
+          <t>9021; 26445</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6603; 18823</t>
+          <t>7215; 19643</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1736; 10403</t>
+          <t>1603; 10506</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3045; 14238</t>
+          <t>3077; 14351</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5377; 19525</t>
+          <t>5196; 17695</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5227; 14054</t>
+          <t>5586; 14314</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11693; 28636</t>
+          <t>11504; 28355</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8933; 23975</t>
+          <t>8499; 24058</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17915; 38795</t>
+          <t>17420; 39149</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14416; 29531</t>
+          <t>15467; 29854</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17792</t>
+          <t>17885</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15429</t>
+          <t>15543</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>33221</t>
+          <t>33428</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11939; 28729</t>
+          <t>11275; 29183</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14835; 36944</t>
+          <t>15153; 36751</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17475; 40263</t>
+          <t>16774; 39366</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10870; 28478</t>
+          <t>10803; 28221</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8266; 22407</t>
+          <t>8716; 23739</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18900; 38809</t>
+          <t>19794; 41614</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9956; 26452</t>
+          <t>9957; 26765</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10066; 23668</t>
+          <t>10185; 23606</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23597; 47127</t>
+          <t>24117; 45515</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38835; 69027</t>
+          <t>37548; 69098</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31097; 56818</t>
+          <t>30705; 56875</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23936; 45917</t>
+          <t>24592; 46969</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13145</t>
+          <t>12887</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12300</t>
+          <t>12315</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25445</t>
+          <t>25202</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8669; 23582</t>
+          <t>7967; 24310</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5259; 19960</t>
+          <t>4911; 18639</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5660; 17743</t>
+          <t>5226; 18201</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7615; 19775</t>
+          <t>7871; 19857</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1011; 10264</t>
+          <t>1001; 10667</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4135; 18901</t>
+          <t>5093; 19449</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4933; 18152</t>
+          <t>4962; 18598</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7256; 18808</t>
+          <t>7609; 19586</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10732; 28407</t>
+          <t>11468; 29015</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12289; 32694</t>
+          <t>12480; 31851</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13149; 31221</t>
+          <t>11877; 30619</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18053; 35254</t>
+          <t>17919; 34644</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21577</t>
+          <t>22675</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>28815</t>
+          <t>31239</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>50392</t>
+          <t>53915</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2887; 13163</t>
+          <t>2804; 13146</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8186; 25709</t>
+          <t>8209; 24694</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15837; 34667</t>
+          <t>16051; 34806</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13071; 35103</t>
+          <t>13617; 36313</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10223; 25757</t>
+          <t>10421; 25300</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10103; 26527</t>
+          <t>11001; 27917</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17918; 39276</t>
+          <t>18745; 39824</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17722; 42065</t>
+          <t>23957; 44903</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15546; 35065</t>
+          <t>15233; 34554</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22163; 44914</t>
+          <t>21699; 44386</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37098; 66722</t>
+          <t>38388; 69184</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>34857; 69575</t>
+          <t>43048; 70870</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14642</t>
+          <t>15789</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23752</t>
+          <t>25107</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>40896</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4513; 17423</t>
+          <t>4958; 17579</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3329; 15265</t>
+          <t>3207; 14330</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2572; 13744</t>
+          <t>2566; 13762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9862; 21317</t>
+          <t>10384; 22451</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7058; 21149</t>
+          <t>6421; 20696</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8199; 23051</t>
+          <t>8112; 23490</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1123; 11227</t>
+          <t>1125; 9708</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>12464; 32388</t>
+          <t>19346; 31580</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14042; 33822</t>
+          <t>14215; 34003</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13908; 33152</t>
+          <t>14820; 32782</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5206; 20189</t>
+          <t>5474; 19394</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>26373; 48083</t>
+          <t>32606; 49845</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10151</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>6593</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16957</t>
+          <t>17143</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2908; 14120</t>
+          <t>2921; 14174</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6241; 19827</t>
+          <t>6248; 20064</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2486; 13782</t>
+          <t>2580; 12701</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6275; 16435</t>
+          <t>6353; 17067</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1982; 11369</t>
+          <t>1934; 11110</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8055; 23591</t>
+          <t>8234; 23374</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1011; 10418</t>
+          <t>1012; 9481</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3669; 11022</t>
+          <t>3770; 11891</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6897; 20867</t>
+          <t>6904; 20244</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16879; 37061</t>
+          <t>16841; 36620</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4937; 17724</t>
+          <t>4936; 18407</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11144; 24646</t>
+          <t>11925; 24436</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46799</t>
+          <t>54240</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>50688</t>
+          <t>62750</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>97487</t>
+          <t>116990</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11304; 29170</t>
+          <t>11312; 28168</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15717; 35505</t>
+          <t>15738; 36151</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8543; 24010</t>
+          <t>8594; 24458</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>35413; 60652</t>
+          <t>41137; 70506</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6361; 21054</t>
+          <t>6531; 21505</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20614; 42632</t>
+          <t>20217; 43807</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10946; 27332</t>
+          <t>10569; 27657</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>24434; 71838</t>
+          <t>51253; 77053</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>21258; 43363</t>
+          <t>22427; 45283</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>40091; 71518</t>
+          <t>40414; 69646</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23974; 46369</t>
+          <t>24165; 45931</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>61349; 121899</t>
+          <t>100310; 137581</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>45061</t>
+          <t>50871</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>64307</t>
+          <t>73123</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>109369</t>
+          <t>123994</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>14989; 33991</t>
+          <t>15010; 35424</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>16139; 38211</t>
+          <t>15947; 37191</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7216; 21949</t>
+          <t>7125; 22142</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19161; 66335</t>
+          <t>38918; 65228</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>14934; 35767</t>
+          <t>15209; 34721</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11943; 31066</t>
+          <t>11562; 29570</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9484; 27135</t>
+          <t>8592; 27104</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>52410; 76209</t>
+          <t>61467; 88277</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>35615; 62063</t>
+          <t>35392; 62154</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>32559; 61612</t>
+          <t>31006; 60599</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>19709; 41880</t>
+          <t>19789; 42496</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>67168; 135601</t>
+          <t>106864; 145124</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>180994</t>
+          <t>197102</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>210781</t>
+          <t>236290</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>391775</t>
+          <t>433392</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>92818; 134187</t>
+          <t>93850; 134078</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>104290; 149818</t>
+          <t>104014; 153414</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>97872; 140840</t>
+          <t>97222; 140278</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>144690; 213009</t>
+          <t>174010; 226084</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>76264; 114793</t>
+          <t>75676; 112191</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>119979; 166399</t>
+          <t>116341; 164928</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>86925; 129041</t>
+          <t>86840; 130473</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>172014; 238691</t>
+          <t>213731; 260319</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>180170; 236111</t>
+          <t>179404; 232890</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>236250; 304336</t>
+          <t>234629; 305274</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>197047; 254881</t>
+          <t>198917; 256454</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>340406; 436642</t>
+          <t>402625; 471890</t>
         </is>
       </c>
     </row>
